--- a/exports/trend_1d/KFINTECH_full_report.xlsx
+++ b/exports/trend_1d/KFINTECH_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:U25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>10.27</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44957</v>
+        <v>44958</v>
       </c>
       <c r="H2" t="n">
-        <v>319.7</v>
+        <v>308.05</v>
       </c>
       <c r="I2" t="n">
         <v>311.189611191665</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.77</v>
+        <v>-6.31</v>
       </c>
       <c r="L2" t="n">
-        <v>4.9</v>
+        <v>7.39</v>
       </c>
       <c r="M2" t="n">
         <v>0.76</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>13.53</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>45037</v>
+        <v>45040</v>
       </c>
       <c r="H3" t="n">
-        <v>297.2</v>
+        <v>309.55</v>
       </c>
       <c r="I3" t="n">
         <v>304.0167431786822</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K3" t="n">
-        <v>3.52</v>
+        <v>-0.49</v>
       </c>
       <c r="L3" t="n">
         <v>6.83</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>11.06</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>45278</v>
+        <v>45279</v>
       </c>
       <c r="H4" t="n">
-        <v>512.9</v>
+        <v>488.2</v>
       </c>
       <c r="I4" t="n">
         <v>491.9432336812543</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K4" t="n">
-        <v>65.69</v>
+        <v>57.71</v>
       </c>
       <c r="L4" t="n">
         <v>3.52</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>164</v>
+        <v>165</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>9</v>
+      </c>
+      <c r="U4" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>16.27</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>45309</v>
+        <v>45310</v>
       </c>
       <c r="H5" t="n">
-        <v>538.25</v>
+        <v>542.85</v>
       </c>
       <c r="I5" t="n">
         <v>542.0428030808632</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K5" t="n">
-        <v>-10.25</v>
+        <v>-11.19</v>
       </c>
       <c r="L5" t="n">
-        <v>11.8</v>
+        <v>11.84</v>
       </c>
       <c r="M5" t="n">
         <v>1.44</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>8.050000000000001</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>45358</v>
+        <v>45362</v>
       </c>
       <c r="H6" t="n">
-        <v>651.25</v>
+        <v>628.05</v>
       </c>
       <c r="I6" t="n">
         <v>635.0148258118414</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="K6" t="n">
-        <v>19.97</v>
+        <v>15.69</v>
       </c>
       <c r="L6" t="n">
         <v>0.76</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>16.4</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>45407</v>
+        <v>45408</v>
       </c>
       <c r="H7" t="n">
-        <v>660.75</v>
+        <v>693.45</v>
       </c>
       <c r="I7" t="n">
         <v>676.297332992721</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.21</v>
+        <v>-10.41</v>
       </c>
       <c r="L7" t="n">
-        <v>7.28</v>
+        <v>11.77</v>
       </c>
       <c r="M7" t="n">
         <v>2.1</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>12.13</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>45441</v>
+        <v>45442</v>
       </c>
       <c r="H8" t="n">
-        <v>743.9</v>
+        <v>678.3</v>
       </c>
       <c r="I8" t="n">
         <v>698.3230508861373</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K8" t="n">
-        <v>7.28</v>
+        <v>-2.18</v>
       </c>
       <c r="L8" t="n">
         <v>4.53</v>
       </c>
       <c r="M8" t="n">
-        <v>0.85</v>
+        <v>1.87</v>
       </c>
       <c r="N8" t="n">
-        <v>3.64</v>
+        <v>8.82</v>
       </c>
       <c r="O8" t="n">
         <v>4.95</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>17.96</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>45489</v>
+        <v>45491</v>
       </c>
       <c r="H9" t="n">
-        <v>753.1</v>
+        <v>771.8</v>
       </c>
       <c r="I9" t="n">
         <v>770.8829196191928</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K9" t="n">
-        <v>-11.03</v>
+        <v>-13.78</v>
       </c>
       <c r="L9" t="n">
         <v>16.67</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>10.72</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>45589</v>
+        <v>45590</v>
       </c>
       <c r="H10" t="n">
-        <v>977.7</v>
+        <v>943.05</v>
       </c>
       <c r="I10" t="n">
         <v>955.7668965881725</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K10" t="n">
-        <v>26.68</v>
+        <v>22.19</v>
       </c>
       <c r="L10" t="n">
         <v>9.43</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>20.05</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>45618</v>
+        <v>45621</v>
       </c>
       <c r="H11" t="n">
-        <v>1066.7</v>
+        <v>1103.65</v>
       </c>
       <c r="I11" t="n">
         <v>1097.277261895047</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K11" t="n">
-        <v>-13.11</v>
+        <v>-17.03</v>
       </c>
       <c r="L11" t="n">
-        <v>15</v>
+        <v>18.1</v>
       </c>
       <c r="M11" t="n">
         <v>5.49</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>12.25</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>45667</v>
+        <v>45670</v>
       </c>
       <c r="H12" t="n">
-        <v>1377.7</v>
+        <v>1255.15</v>
       </c>
       <c r="I12" t="n">
         <v>1307.880648306068</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K12" t="n">
-        <v>24.83</v>
+        <v>13.73</v>
       </c>
       <c r="L12" t="n">
         <v>2.38</v>
@@ -1125,7 +1268,7 @@
         <v>2.66</v>
       </c>
       <c r="N12" t="n">
-        <v>5.12</v>
+        <v>8.9</v>
       </c>
       <c r="O12" t="n">
         <v>3.46</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>24.46</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>45736</v>
+        <v>45737</v>
       </c>
       <c r="H13" t="n">
-        <v>1050.3</v>
+        <v>1100.5</v>
       </c>
       <c r="I13" t="n">
         <v>1061.099100691053</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K13" t="n">
-        <v>16.32</v>
+        <v>12.32</v>
       </c>
       <c r="L13" t="n">
         <v>8.16</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>17.38</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45782</v>
+        <v>45783</v>
       </c>
       <c r="H14" t="n">
-        <v>1087.8</v>
+        <v>1041.7</v>
       </c>
       <c r="I14" t="n">
         <v>1050.858540460731</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.15</v>
+        <v>-5.34</v>
       </c>
       <c r="L14" t="n">
         <v>24.69</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>23.06</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45812</v>
+        <v>45813</v>
       </c>
       <c r="H15" t="n">
-        <v>1170.3</v>
+        <v>1206.1</v>
       </c>
       <c r="I15" t="n">
         <v>1194.719830825856</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K15" t="n">
-        <v>-12.35</v>
+        <v>-15.78</v>
       </c>
       <c r="L15" t="n">
-        <v>12.8</v>
+        <v>16.64</v>
       </c>
       <c r="M15" t="n">
         <v>4.83</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>12.9</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45862</v>
+        <v>45863</v>
       </c>
       <c r="H16" t="n">
-        <v>1232.6</v>
+        <v>1164.6</v>
       </c>
       <c r="I16" t="n">
         <v>1186.48966509808</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K16" t="n">
-        <v>2.2</v>
+        <v>-3.44</v>
       </c>
       <c r="L16" t="n">
-        <v>3.52</v>
+        <v>5.56</v>
       </c>
       <c r="M16" t="n">
-        <v>2.01</v>
+        <v>2.56</v>
       </c>
       <c r="N16" t="n">
-        <v>3.85</v>
+        <v>5.52</v>
       </c>
       <c r="O16" t="n">
         <v>3.06</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>11.93</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="H17" t="n">
-        <v>1117.6</v>
+        <v>1144.8</v>
       </c>
       <c r="I17" t="n">
         <v>1139.738432300599</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K17" t="n">
-        <v>4.04</v>
+        <v>1.7</v>
       </c>
       <c r="L17" t="n">
         <v>3.73</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>7.94</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="H18" t="n">
-        <v>1080.4</v>
+        <v>1060.7</v>
       </c>
       <c r="I18" t="n">
         <v>1074.649740785416</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K18" t="n">
-        <v>-5.63</v>
+        <v>-7.35</v>
       </c>
       <c r="L18" t="n">
-        <v>6.36</v>
+        <v>7.58</v>
       </c>
       <c r="M18" t="n">
         <v>0.17</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>9.619999999999999</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="H19" t="n">
-        <v>1072.5</v>
+        <v>1143.8</v>
       </c>
       <c r="I19" t="n">
         <v>1132.066273722307</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.11</v>
+        <v>-7.83</v>
       </c>
       <c r="L19" t="n">
-        <v>3.11</v>
+        <v>8.32</v>
       </c>
       <c r="M19" t="n">
-        <v>0.92</v>
+        <v>1.63</v>
       </c>
       <c r="N19" t="n">
-        <v>2.73</v>
+        <v>6.65</v>
       </c>
       <c r="O19" t="n">
         <v>-1.82</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>11.29</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="H20" t="n">
-        <v>1102.8</v>
+        <v>1069.4</v>
       </c>
       <c r="I20" t="n">
         <v>1087.736248223955</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.58</v>
+        <v>-6.5</v>
       </c>
       <c r="L20" t="n">
-        <v>5.11</v>
+        <v>6.8</v>
       </c>
       <c r="M20" t="n">
         <v>0.9</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>11.07</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="H21" t="n">
-        <v>975.1</v>
+        <v>996.95</v>
       </c>
       <c r="I21" t="n">
         <v>989.7145612050275</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K21" t="n">
-        <v>8.82</v>
+        <v>6.77</v>
       </c>
       <c r="L21" t="n">
         <v>5.33</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>112</v>
+        <v>113</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>6</v>
+      </c>
+      <c r="U21" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>10.77</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="H22" t="n">
-        <v>895.7</v>
+        <v>863.95</v>
       </c>
       <c r="I22" t="n">
         <v>894.7649949767226</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K22" t="n">
-        <v>-10.16</v>
+        <v>-13.34</v>
       </c>
       <c r="L22" t="n">
-        <v>10.53</v>
+        <v>14.07</v>
       </c>
       <c r="M22" t="n">
         <v>4.2</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>14.66</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="H23" t="n">
-        <v>861.75</v>
+        <v>898.45</v>
       </c>
       <c r="I23" t="n">
         <v>891.0870112424906</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K23" t="n">
-        <v>0.25</v>
+        <v>-3.99</v>
       </c>
       <c r="L23" t="n">
         <v>8.58</v>
@@ -1752,7 +2027,7 @@
         <v>2.21</v>
       </c>
       <c r="N23" t="n">
-        <v>3.76</v>
+        <v>4.26</v>
       </c>
       <c r="O23" t="n">
         <v>-3.54</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>10.91</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="H24" t="n">
-        <v>900</v>
+        <v>884.8</v>
       </c>
       <c r="I24" t="n">
         <v>889.6537532607319</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="K24" t="n">
-        <v>0.17</v>
+        <v>-1.52</v>
       </c>
       <c r="L24" t="n">
         <v>6.73</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1869,6 +2168,14 @@
       <c r="Q25" t="n">
         <v>30</v>
       </c>
+      <c r="R25" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3597,7 +3904,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56.6</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="6">
@@ -3607,7 +3914,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
@@ -3617,7 +3924,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8">
@@ -3627,7 +3934,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -3637,7 +3944,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10">
@@ -3647,7 +3954,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>95.59999999999999</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="11">
@@ -3657,7 +3964,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -3667,7 +3974,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -3677,7 +3984,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34.8</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="14">
@@ -3687,7 +3994,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.5</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="15">
@@ -3697,7 +4004,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10.29</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="16">
@@ -3707,7 +4014,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-1.83</v>
+        <v>-5.43</v>
       </c>
     </row>
     <row r="17">
@@ -3717,7 +4024,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>65.69</v>
+        <v>57.71</v>
       </c>
     </row>
     <row r="18">
@@ -3727,7 +4034,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52.2</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="19">
@@ -3737,7 +4044,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.9</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="20">
@@ -3747,7 +4054,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.73</v>
+        <v>7.58</v>
       </c>
     </row>
     <row r="21">
@@ -3767,7 +4074,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -3777,7 +4084,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -3787,7 +4094,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.19</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="25">
@@ -3807,7 +4114,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.04</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="27">
@@ -3817,7 +4124,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8.35</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="28">
@@ -3827,7 +4134,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
